--- a/output/details/2026-05-22/preprocessed_data.xlsx
+++ b/output/details/2026-05-22/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46164</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1133411251026238</v>
+        <v>-0.1172766662722982</v>
       </c>
       <c r="C2" t="n">
-        <v>0.156263894284753</v>
+        <v>-0.1393889473958931</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1560484927503001</v>
+        <v>-0.1391152205387594</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1215491834913165</v>
+        <v>0.00310926223335979</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00169946801379673</v>
+        <v>0.00169641170936251</v>
       </c>
       <c r="G2" t="n">
-        <v>1.919044105237549</v>
+        <v>2.484077022125744</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4432316299116986</v>
+        <v>-0.2687668425294781</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
